--- a/data/trans_bre/P34A_R-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P34A_R-Clase-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,73; 8,97</t>
+          <t>-5,32; 8,85</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 11,65</t>
+          <t>-0,7; 11,59</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,28; 10,21</t>
+          <t>-3,43; 9,64</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-9,23; 1,21</t>
+          <t>-9,36; 1,42</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-15,0; 29,12</t>
+          <t>-13,86; 28,11</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 89,5</t>
+          <t>-3,92; 87,6</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-11,63; 46,59</t>
+          <t>-12,5; 42,59</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-30,9; 5,11</t>
+          <t>-31,32; 5,79</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,45; 19,81</t>
+          <t>5,99; 19,8</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,67; 14,79</t>
+          <t>1,62; 14,38</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 11,93</t>
+          <t>-0,59; 12,33</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,69; 13,11</t>
+          <t>1,55; 13,31</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>15,72; 75,16</t>
+          <t>17,55; 73,75</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,29; 100,22</t>
+          <t>7,2; 90,25</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-7,63; 51,82</t>
+          <t>-1,88; 53,74</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,74; 57,91</t>
+          <t>4,95; 59,36</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,4; 8,5</t>
+          <t>-8,92; 9,23</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,87; 16,52</t>
+          <t>3,17; 17,07</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 14,13</t>
+          <t>-4,54; 14,3</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,84; 35,9</t>
+          <t>0,27; 33,6</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-17,51; 19,44</t>
+          <t>-18,51; 20,69</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,22; 71,59</t>
+          <t>11,43; 75,03</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-9,69; 41,2</t>
+          <t>-11,89; 41,3</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,17; 381,47</t>
+          <t>0,18; 338,94</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,42; 5,14</t>
+          <t>-4,6; 4,42</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,92; 9,51</t>
+          <t>1,25; 9,94</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 8,64</t>
+          <t>-0,68; 8,89</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-23,54; 2,42</t>
+          <t>-22,95; 3,01</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-8,97; 11,55</t>
+          <t>-9,56; 9,78</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,36; 40,08</t>
+          <t>4,35; 41,64</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 23,76</t>
+          <t>-1,68; 24,35</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-57,61; 6,58</t>
+          <t>-58,68; 8,51</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 10,09</t>
+          <t>-3,61; 10,38</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,61; 13,98</t>
+          <t>3,29; 14,19</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,29; 12,66</t>
+          <t>1,51; 12,42</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-10,22; 9,93</t>
+          <t>-8,49; 10,42</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-6,61; 21,69</t>
+          <t>-6,67; 22,18</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,7; 56,24</t>
+          <t>10,43; 58,89</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,24; 33,72</t>
+          <t>3,54; 33,44</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-22,31; 23,94</t>
+          <t>-18,78; 25,62</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>20,62; 31,2</t>
+          <t>20,44; 30,88</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>13,1; 23,07</t>
+          <t>13,63; 23,33</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>24,03; 34,83</t>
+          <t>23,8; 35,06</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>23,02; 43,18</t>
+          <t>23,98; 43,21</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>87,86; 207,67</t>
+          <t>85,92; 199,14</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>80,07; 267,13</t>
+          <t>83,92; 279,48</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>108,16; 249,93</t>
+          <t>109,2; 262,89</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>88,32; 578,41</t>
+          <t>88,49; 587,6</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,75; 7,58</t>
+          <t>2,77; 7,43</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,31; 10,54</t>
+          <t>6,33; 10,59</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,31; 11,16</t>
+          <t>6,45; 11,1</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,51; 13,86</t>
+          <t>0,48; 14,08</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,46; 19,08</t>
+          <t>6,43; 18,47</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>26,39; 48,77</t>
+          <t>27,17; 49,6</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,76; 34,23</t>
+          <t>18,7; 34,11</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,73; 56,41</t>
+          <t>3,18; 53,3</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P34A_R-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P34A_R-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-3,89</t>
+          <t>-3,44</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-14,36%</t>
+          <t>-12,8%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,32; 8,85</t>
+          <t>-5,16; 9,21</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 11,59</t>
+          <t>-0,1; 11,95</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 9,64</t>
+          <t>-3,48; 10,03</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-9,36; 1,42</t>
+          <t>-8,08; 2,28</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-13,86; 28,11</t>
+          <t>-14,11; 28,53</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 87,6</t>
+          <t>-1,19; 93,24</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-12,5; 42,59</t>
+          <t>-12,17; 45,18</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-31,32; 5,79</t>
+          <t>-27,72; 9,5</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7,28</t>
+          <t>7,37</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,84%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,99; 19,8</t>
+          <t>5,51; 19,92</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,62; 14,38</t>
+          <t>1,66; 14,66</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 12,33</t>
+          <t>-1,03; 12,42</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,55; 13,31</t>
+          <t>1,67; 13,65</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>17,55; 73,75</t>
+          <t>16,02; 75,9</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,2; 90,25</t>
+          <t>7,8; 100,26</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 53,74</t>
+          <t>-4,2; 55,45</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,95; 59,36</t>
+          <t>5,93; 63,24</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>16,77</t>
+          <t>4,64</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>70,52%</t>
+          <t>12,51%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,92; 9,23</t>
+          <t>-8,41; 9,22</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,17; 17,07</t>
+          <t>2,61; 17,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 14,3</t>
+          <t>-3,97; 14,4</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,27; 33,6</t>
+          <t>-2,7; 11,88</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-18,51; 20,69</t>
+          <t>-17,21; 21,69</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,43; 75,03</t>
+          <t>9,12; 72,67</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-11,89; 41,3</t>
+          <t>-10,28; 41,65</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,18; 338,94</t>
+          <t>-7,22; 34,88</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-6,96</t>
+          <t>2,54</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-18,14%</t>
+          <t>6,69%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,6; 4,42</t>
+          <t>-4,34; 4,65</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,25; 9,94</t>
+          <t>0,97; 9,53</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 8,89</t>
+          <t>-0,25; 8,89</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-22,95; 3,01</t>
+          <t>-1,56; 6,68</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-9,56; 9,78</t>
+          <t>-8,88; 10,36</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,35; 41,64</t>
+          <t>3,45; 40,29</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 24,35</t>
+          <t>-0,88; 24,49</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-58,68; 8,51</t>
+          <t>-3,95; 18,61</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2,17</t>
+          <t>1,54</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>3,49%</t>
         </is>
       </c>
     </row>
@@ -1060,49 +1060,49 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 10,38</t>
+          <t>-4,15; 9,55</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,29; 14,19</t>
+          <t>3,4; 14,09</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,51; 12,42</t>
+          <t>1,14; 12,67</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,49; 10,42</t>
+          <t>-3,95; 6,14</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-6,67; 22,18</t>
+          <t>-7,56; 20,29</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,43; 58,89</t>
+          <t>10,58; 56,83</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,54; 33,44</t>
+          <t>2,6; 33,53</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-18,78; 25,62</t>
+          <t>-8,09; 15,04</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>35,86</t>
+          <t>36,72</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>268,0%</t>
+          <t>303,34%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>20,44; 30,88</t>
+          <t>20,18; 30,69</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>13,63; 23,33</t>
+          <t>13,35; 23,22</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>23,8; 35,06</t>
+          <t>23,57; 34,74</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>23,98; 43,21</t>
+          <t>26,1; 43,12</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>85,92; 199,14</t>
+          <t>85,91; 200,53</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>83,92; 279,48</t>
+          <t>84,22; 275,35</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>109,2; 262,89</t>
+          <t>104,65; 245,75</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>88,49; 587,6</t>
+          <t>111,01; 613,02</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7,05</t>
+          <t>6,94</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>20,69%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,77; 7,43</t>
+          <t>2,77; 7,59</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,33; 10,59</t>
+          <t>6,06; 10,49</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,45; 11,1</t>
+          <t>6,39; 11,33</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,48; 14,08</t>
+          <t>4,4; 9,35</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,43; 18,47</t>
+          <t>6,47; 19,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>27,17; 49,6</t>
+          <t>26,0; 48,24</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,7; 34,11</t>
+          <t>18,22; 34,75</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,18; 53,3</t>
+          <t>12,96; 29,11</t>
         </is>
       </c>
     </row>
